--- a/04_DESIGN_TABLES/DesignTable_2403LH.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2403LH.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -529,6 +529,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1423,24 +1428,47 @@
           <t>2403-LH-24-24</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.875</v>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>2403-LH-24-24</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1 7/8-12 x 1 7/8-12 (male JIC, large hex)</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1@DRIVE: Brennan TFA catalog p5 table TFA-p005-t02 "2403-LH MJ-MJ STRAIGHT LARGE HEX" row 2403-LH-24-24 col "L LGTH" = "2.75" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 575.7, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p5 2403-LH drawing: L = overall, C HEX = the large body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 16/16 rows with an Air-Way/OMi value agree with this catalog column to rounding; C2HEX@HEX: Brennan TFA catalog p5 table TFA-p005-t02 "2403-LH MJ-MJ STRAIGHT LARGE HEX" row 2403-LH-24-24 col "C HEX" = "2.125" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 575.7, page verified) [Brennan = yes 2026-10-18] - large body hex; mapping: TFA p5 2403-LH drawing: L = overall, C HEX = the large body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 16/16 rows with an Air-Way/OMi value agree with this catalog column to rounding; D1@BORE: Brennan TFA catalog p5 table TFA-p005-t02 "2403-LH MJ-MJ STRAIGHT LARGE HEX" row 2403-LH-24-24 col "B1 DRILL" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 575.7, page verified) [Brennan = yes 2026-10-18] - bore end B1; mapping: TFA p5 2403-LH drawing: L = overall, C HEX = the large body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 16/16 rows with an Air-Way/OMi value agree with this catalog column to rounding; D2@BORE: Brennan TFA catalog p5 table TFA-p005-t02 "2403-LH MJ-MJ STRAIGHT LARGE HEX" row 2403-LH-24-24 col "B2 DRILL" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 575.7, page verified) [Brennan = yes 2026-10-18] - bore end B2; mapping: TFA p5 2403-LH drawing: L = overall, C HEX = the large body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 16/16 rows with an Air-Way/OMi value agree with this catalog column to rounding; THDMAJ_B1@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (1 7/8-12); THDMAJ_B2@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (1 7/8-12); $PRP@Threads: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread texts, format of the built 2403LH rows</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L1 / large hex / bores from the Brennan TFA catalog p5 alone; JIC ends from the 2403 end library (load_2403 fold)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1451,6 +1479,11 @@
       <c r="N19" t="inlineStr">
         <is>
           <t>2403-LH-24-24</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
